--- a/source/Translation.xlsx
+++ b/source/Translation.xlsx
@@ -50280,7 +50280,7 @@
       </x:c>
       <x:c r="E394" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">File size {0} is larger than allowed maxiumum of {1}</x:t>
+          <x:t xml:space="preserve">File size {0} is larger than allowed maximum of {1}</x:t>
         </x:is>
       </x:c>
       <x:c r="F394" t="inlineStr">
@@ -50360,7 +50360,7 @@
       </x:c>
       <x:c r="U394" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Dimensiunea fișierului {0} este mai mare decât permisiunea maxiumum din {1}</x:t>
+          <x:t xml:space="preserve">Dimensiunea fișierului {0} este mai mare decât permisiunea maximum din {1}</x:t>
         </x:is>
       </x:c>
       <x:c r="V394" t="inlineStr">
